--- a/public/outils/matrices/tableau-amortissement-et-comparateur-de-prets.xlsx
+++ b/public/outils/matrices/tableau-amortissement-et-comparateur-de-prets.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="491">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -54,7 +54,7 @@
     <t>Il calcule la mensualité, l'échéancier complet sur 30 ans au plus (intérêts, capital, assurance, capital restant dû à chaque date), le coût total du crédit, le TAEG réglementaire face au taux d'usure, le taux d'effort au sens du HCSF (Haut Conseil de stabilité financière, l'autorité qui fixe les normes d'octroi des banques) et ce qu'il faudrait payer pour solder le prêt à une date donnée. Le comparateur met trois offres côte à côte et les classe par TAEG et par coût total.</t>
   </si>
   <si>
-    <t>Deux onglets de saisie seulement : Mon prêt pour un prêt, Comparateur pour trois offres. Vous remplissez les cellules bleues, le reste se calcule.</t>
+    <t>Deux onglets de saisie seulement : Mon prêt pour un prêt, Comparateur pour trois offres. Vous remplissez les cellules violettes, le reste se calcule.</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -177,7 +177,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu ciel, texte bleu nuit</t>
+    <t>Fond violet clair, texte violet sombre</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -195,7 +195,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond presque blanc, texte bleu nuit en gras</t>
+    <t>Fond presque blanc, texte violet sombre en gras</t>
   </si>
   <si>
     <t>Résultat de bloc, chiffre clé</t>
@@ -204,7 +204,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section, en-tête de tableau</t>
@@ -231,7 +231,7 @@
     <t>Rouge : lisez le commentaire de la ligne et corrigez. Un contrôle sans objet reste gris.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules bleues, elles, restent modifiables et effaçables sans rien déverrouiller : n'ôtez la protection que pour toucher une cellule blanche, par l'onglet Révision, « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules violettes, elles, restent modifiables et effaçables sans rien déverrouiller : n'ôtez la protection que pour toucher une cellule blanche, par l'onglet Révision, « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -252,7 +252,7 @@
     <t>Mon prêt!C7:C16, Mon prêt!C41, Mon prêt!C47 ; Comparateur!C8:E16</t>
   </si>
   <si>
-    <t>Le classeur est livré rempli d'un exemple (un prêt de 180 000 € sur 25 ans, trois offres). Gardez-le pour vous repérer, ou effacez toutes les cellules bleues avant de saisir votre dossier : la touche Suppr suffit, la protection de la feuille ne s'y oppose pas. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être dans votre cas : le différé (Mon prêt!C10), le versement au FMG, c'est-à-dire au fonds mutuel de garantie d'une caution (Mon prêt!C16), les revenus (Mon prêt!C41), le mois de remboursement anticipé (Mon prêt!C47), et la colonne E du Comparateur si vous n'avez que deux offres. Pendant que vous effacez, Mon prêt!C17 passe au rouge et les résultats se vident : c'est normal, tout revient dès que la saisie est complète.</t>
+    <t>Le classeur est livré rempli d'un exemple (un prêt de 180 000 € sur 25 ans, trois offres). Gardez-le pour vous repérer, ou effacez toutes les cellules violettes avant de saisir votre dossier : la touche Suppr suffit, la protection de la feuille ne s'y oppose pas. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être dans votre cas : le différé (Mon prêt!C10), le versement au FMG, c'est-à-dire au fonds mutuel de garantie d'une caution (Mon prêt!C16), les revenus (Mon prêt!C41), le mois de remboursement anticipé (Mon prêt!C47), et la colonne E du Comparateur si vous n'avez que deux offres. Pendant que vous effacez, Mon prêt!C17 passe au rouge et les résultats se vident : c'est normal, tout revient dès que la saisie est complète.</t>
   </si>
   <si>
     <t>Une saisie résiduelle de l'exemple est l'erreur la plus probable d'un premier usage : un différé ou un FMG hérités changent la mensualité et le coût net sans que rien ne le signale.</t>
@@ -363,7 +363,7 @@
     <t>Chaque trimestre, mettez à jour les trois taux d'usure (Paramètres!C8:C10, Banque de France), puis le trimestre et la date de l'avis (Paramètres!C41 et Paramètres!C42) et la date de vérification (Paramètres!C43). Les repères de taux (Paramètres!C25 et Paramètres!C26) bougent chaque mois : rafraîchissez-les avant tout dossier engageant. Les repères d'assurance et de frais (Paramètres!C27:C32), une fois par an. Source : banque-france.fr, rubrique Taux d'usure, avis publié le dernier jour ouvré de mars, juin, septembre et décembre.</t>
   </si>
   <si>
-    <t>Un taux d'usure périmé fausse le contrôle d'usure sans prévenir. Toutes les formules pointent ici, et les libellés de source de Paramètres et de Méthode se mettent à jour seuls à partir du trimestre et des dates saisis : ce sont des cellules bleues, rien à déverrouiller.</t>
+    <t>Un taux d'usure périmé fausse le contrôle d'usure sans prévenir. Toutes les formules pointent ici, et les libellés de source de Paramètres et de Méthode se mettent à jour seuls à partir du trimestre et des dates saisis : ce sont des cellules violettes, rien à déverrouiller.</t>
   </si>
   <si>
     <t xml:space="preserve">  EXEMPLE GUIDÉ</t>
@@ -477,10 +477,10 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les benchmarks (taux d'usure, normes HCSF, plafond d'indemnité, part de FMG restituée, repères de taux, d'assurance et de garantie) changent avec la réglementation ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (montant, taux, durée, assurance, frais, revenus, offres) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les benchmarks (taux d'usure, normes HCSF, plafond d'indemnité, part de FMG restituée, repères de taux, d'assurance et de garantie) changent avec la réglementation ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (montant, taux, durée, assurance, frais, revenus, offres) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
-    <t>Tout se met à jour dans des cellules bleues, sans ôter la protection : les libellés de source de Paramètres et de Méthode se reconstruisent seuls à partir du trimestre, de la date de l'avis et de la date de vérification (Paramètres!C41:C43). Les chiffres cités dans ce guide et dans Méthode, eux, sont écrits en toutes lettres et datés du millésime 2026 : relisez-les à chaque mise à jour de Paramètres, en particulier le taux d'usure de l'exemple guidé, les repères de la colonne « Repère métier » ci-dessus et les ordres de grandeur de garantie de l'étape 1.</t>
+    <t>Tout se met à jour dans des cellules violettes, sans ôter la protection : les libellés de source de Paramètres et de Méthode se reconstruisent seuls à partir du trimestre, de la date de l'avis et de la date de vérification (Paramètres!C41:C43). Les chiffres cités dans ce guide et dans Méthode, eux, sont écrits en toutes lettres et datés du millésime 2026 : relisez-les à chaque mise à jour de Paramètres, en particulier le taux d'usure de l'exemple guidé, les repères de la colonne « Repère métier » ci-dessus et les ordres de grandeur de garantie de l'étape 1.</t>
   </si>
   <si>
     <t>Paramètre</t>
@@ -699,7 +699,7 @@
     <t>Mensualité, coût total, TAEG face au taux d'usure, repères HCSF et capital restant dû à une date donnée.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  L'EMPRUNT</t>
@@ -1537,7 +1537,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1557,19 +1557,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1581,7 +1581,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1594,12 +1594,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1609,7 +1609,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1999,6 +1999,237 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10229850" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10229850" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8943975" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8943975" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11658600" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11658600" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="15906750" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15906750" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13992225" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13992225" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8782050" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8782050" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3333,13 +3564,14 @@
     <mergeCell ref="C87:E87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:D52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3895,6 +4127,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -3931,7 +4164,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF2350C8"/>
+    <tabColor rgb="FF4B3D7C"/>
   </sheetPr>
   <dimension ref="B1:L369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -20669,13 +20902,14 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF0B8578"/>
+    <tabColor rgb="FF8B7CC4"/>
   </sheetPr>
   <dimension ref="B1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -21415,6 +21649,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -49731,6 +49966,7 @@
     <mergeCell ref="B369:T369"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -50326,13 +50562,14 @@
     <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -50433,8 +50670,8 @@
         <v>471</v>
       </c>
       <c r="C14" s="4" t="str">
-        <f>"Le TAEG ne peut pas dépasser le taux d'usure du trimestre, fixé par la Banque de France par tranche de durée (moins de 10 ans, 10 à moins de 20 ans, 20 ans et plus). Le classeur choisit la tranche sel"&amp;"on la durée du prêt et compare. Les valeurs de Paramètres sont celles du "&amp;Paramètres!$C$41&amp;", avis publié le "&amp;TEXT(DAY(Paramètres!$C$42),"00")&amp;"/"&amp;TEXT(MONTH(Paramètres!$C$42),"00")&amp;"/"&amp;YEAR(Paramètres!$C$42)&amp;" : à rafraîchir chaque trimestre, en corrigeant aussi le trimestre et la date de l'avis dans Paramètres, deux cellules bleues dont dépendent tous les libellés de source."</f>
-        <v>Le TAEG ne peut pas dépasser le taux d'usure du trimestre, fixé par la Banque de France par tranche de durée (moins de 10 ans, 10 à moins de 20 ans, 20 ans et plus). Le classeur choisit la tranche selon la durée du prêt et compare. Les valeurs de Paramètres sont celles du 3e trimestre 2026, avis publié le 29/06/2026 : à rafraîchir chaque trimestre, en corrigeant aussi le trimestre et la date de l'avis dans Paramètres, deux cellules bleues dont dépendent tous les libellés de source.</v>
+        <f>"Le TAEG ne peut pas dépasser le taux d'usure du trimestre, fixé par la Banque de France par tranche de durée (moins de 10 ans, 10 à moins de 20 ans, 20 ans et plus). Le classeur choisit la tranche sel"&amp;"on la durée du prêt et compare. Les valeurs de Paramètres sont celles du "&amp;Paramètres!$C$41&amp;", avis publié le "&amp;TEXT(DAY(Paramètres!$C$42),"00")&amp;"/"&amp;TEXT(MONTH(Paramètres!$C$42),"00")&amp;"/"&amp;YEAR(Paramètres!$C$42)&amp;" : à rafraîchir chaque trimestre, en corrigeant aussi le trimestre et la date de l'avis dans Paramètres, deux cellules violettes dont dépendent tous les libellés de source."</f>
+        <v>Le TAEG ne peut pas dépasser le taux d'usure du trimestre, fixé par la Banque de France par tranche de durée (moins de 10 ans, 10 à moins de 20 ans, 20 ans et plus). Le classeur choisit la tranche selon la durée du prêt et compare. Les valeurs de Paramètres sont celles du 3e trimestre 2026, avis publié le 29/06/2026 : à rafraîchir chaque trimestre, en corrigeant aussi le trimestre et la date de l'avis dans Paramètres, deux cellules violettes dont dépendent tous les libellés de source.</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="57" customHeight="1" x14ac:dyDescent="0.35">
@@ -50773,5 +51010,6 @@
     <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>